--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>130696933</v>
       </c>
       <c r="B14" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -2156,11 +2156,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Västanbäck sv, Västanbäck sv, Nrk</t>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>130696933</v>
       </c>
       <c r="B14" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
